--- a/artfynd/A 6398-2026 artfynd.xlsx
+++ b/artfynd/A 6398-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>499821</v>
+        <v>488372</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,34 +703,23 @@
           <t>(L.) Mill.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Järnhällorna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597355.1504032105</v>
+        <v>597321</v>
       </c>
       <c r="R2" t="n">
-        <v>6659632.43584802</v>
+        <v>6659644</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,29 +741,24 @@
           <t>Enåker</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>C-Heb-0135</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-04-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-05-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>i tallskogen längst ifrån huvudvägen</t>
+          <t>invid gamla vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +770,7 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Tallskog</t>
         </is>
@@ -799,15 +778,265 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Floraväkterisamordn C-län</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>499821</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101345</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Järnhällorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>597355</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6659632</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2004-04-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-05-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>i tallskogen längst ifrån huvudvägen</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Karin Wiklund</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Markus Rehnberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>499822</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101345</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Järnhällorna, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>597323</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6659647</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2004-04-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2004-05-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>åskrönet mellersta beståndet</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
